--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>10010805</t>
-  </si>
-  <si>
-    <t>SANIA MNYK GR PCH 2L</t>
+    <t>20099955</t>
+  </si>
+  <si>
+    <t>PANCHOS SAPI.PG 140G</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,55 +28,73 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10000442</t>
-  </si>
-  <si>
-    <t>FORTUNE MYK.GRG RF2L</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20099956</t>
+  </si>
+  <si>
+    <t>PANCHOS PEDAS 140G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20097515</t>
-  </si>
-  <si>
-    <t>IDM POP CORN CRML 75</t>
+    <t>20066374</t>
+  </si>
+  <si>
+    <t>IDM MIX NUTS 80G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138230</t>
-  </si>
-  <si>
-    <t>DORITOS JGG BKR 120G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20046198</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCOLAT 51</t>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>20008798</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY CASHEW 82</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20022908</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY ALMOND 82</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -469,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -595,7 +613,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -615,7 +633,47 @@
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>20099955</t>
-  </si>
-  <si>
-    <t>PANCHOS SAPI.PG 140G</t>
+    <t>20116112</t>
+  </si>
+  <si>
+    <t>MAXICORN BBQ 140G</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,73 +28,46 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20099956</t>
-  </si>
-  <si>
-    <t>PANCHOS PEDAS 140G</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20116110</t>
+  </si>
+  <si>
+    <t>MXCORN ROAST.CR 140G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20066374</t>
-  </si>
-  <si>
-    <t>IDM MIX NUTS 80G</t>
+    <t>20122264</t>
+  </si>
+  <si>
+    <t>CHITATO MI GORENG 65</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
+    <t>20134691</t>
+  </si>
+  <si>
+    <t>TWB CRACKR RAINBOW57</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20008798</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20022908</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY ALMOND 82</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>RT,(E-1.5B)</t>
   </si>
 </sst>
 </file>
@@ -487,13 +460,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -593,15 +566,15 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -610,70 +583,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>20116112</t>
-  </si>
-  <si>
-    <t>MAXICORN BBQ 140G</t>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,46 +28,67 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20116110</t>
-  </si>
-  <si>
-    <t>MXCORN ROAST.CR 140G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
+    <t>20051344</t>
+  </si>
+  <si>
+    <t>FITBAR CHOCOLATE 20G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20122264</t>
-  </si>
-  <si>
-    <t>CHITATO MI GORENG 65</t>
+    <t>20040341</t>
+  </si>
+  <si>
+    <t>FITBAR FRTS RSBRY 20</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20134691</t>
-  </si>
-  <si>
-    <t>TWB CRACKR RAINBOW57</t>
+    <t>20023148</t>
+  </si>
+  <si>
+    <t>TIC TAC SAPI PNGG 80</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-1.5B)</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20040528</t>
+  </si>
+  <si>
+    <t>TIC TAC MIX 80G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -460,13 +481,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -589,6 +610,46 @@
         <v>18</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t/>
   </si>
   <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
+    <t>10001826</t>
+  </si>
+  <si>
+    <t>K/G SALTCHEESE RG200</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,67 +28,34 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20118424</t>
+  </si>
+  <si>
+    <t>KG SALTCHEESE S&amp;S200</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20051344</t>
-  </si>
-  <si>
-    <t>FITBAR CHOCOLATE 20G</t>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 52G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20040341</t>
-  </si>
-  <si>
-    <t>FITBAR FRTS RSBRY 20</t>
+    <t>10003485</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO ALMOND 52G</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>20023148</t>
-  </si>
-  <si>
-    <t>TIC TAC SAPI PNGG 80</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20040528</t>
-  </si>
-  <si>
-    <t>TIC TAC MIX 80G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20052766</t>
-  </si>
-  <si>
-    <t>IDM KCNG METE MDU 80</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -481,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -590,66 +557,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
   <si>
     <t/>
   </si>
   <si>
-    <t>10001826</t>
-  </si>
-  <si>
-    <t>K/G SALTCHEESE RG200</t>
+    <t>20117923</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR ORI2'S</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -31,31 +31,58 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20118424</t>
-  </si>
-  <si>
-    <t>KG SALTCHEESE S&amp;S200</t>
+    <t>20117928</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR SPCY2S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>20052391</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE K/S CUP81</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
+    <t>20098059</t>
+  </si>
+  <si>
+    <t>ROMA SNDW PEANUT 157</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>20073409</t>
+  </si>
+  <si>
+    <t>ROMA SANDW CKLT 157G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20008798</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY CASHEW 82</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20022908</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY ALMOND 82</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -448,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -557,6 +584,66 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t/>
   </si>
   <si>
-    <t>20117923</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR ORI2'S</t>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -31,58 +31,40 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20117928</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR SPCY2S</t>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20052391</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE K/S CUP81</t>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20098059</t>
-  </si>
-  <si>
-    <t>ROMA SNDW PEANUT 157</t>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP AYM BWG 5'S</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20073409</t>
-  </si>
-  <si>
-    <t>ROMA SANDW CKLT 157G</t>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 5'S</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>20008798</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20022908</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY ALMOND 82</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -475,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -604,46 +586,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t/>
   </si>
   <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
+    <t>20120796</t>
+  </si>
+  <si>
+    <t>GRUDA ROSTA JG.B 95</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -31,40 +31,61 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20125555</t>
-  </si>
-  <si>
-    <t>SEDAP MI KRN CH/BL86</t>
+    <t>20139132</t>
+  </si>
+  <si>
+    <t>GRUDA RS.MAX B&amp;S 80G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
+    <t>20134686</t>
+  </si>
+  <si>
+    <t>IDM KCG PISTACHIO 55</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20140674</t>
-  </si>
-  <si>
-    <t>SEDAAP AYM BWG 5'S</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20128291</t>
+  </si>
+  <si>
+    <t>IDM KCG ALMD MADU 65</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 5'S</t>
+    <t>20056977</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA BWG 95</t>
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>20089490</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA PDS 90G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20095753</t>
+  </si>
+  <si>
+    <t>GRUDA ROSTA WGYU 95</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -457,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -543,15 +564,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -560,18 +581,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -580,9 +601,49 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20120796</t>
-  </si>
-  <si>
-    <t>GRUDA ROSTA JG.B 95</t>
+    <t>20096682</t>
+  </si>
+  <si>
+    <t>IDM KACANG JUMBO 80</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,64 +28,58 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 52G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20139132</t>
-  </si>
-  <si>
-    <t>GRUDA RS.MAX B&amp;S 80G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20134686</t>
-  </si>
-  <si>
-    <t>IDM KCG PISTACHIO 55</t>
+    <t>10003485</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO ALMOND 52G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20128291</t>
-  </si>
-  <si>
-    <t>IDM KCG ALMD MADU 65</t>
+    <t>10036934</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 40G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20056977</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA BWG 95</t>
+    <t>20114756</t>
+  </si>
+  <si>
+    <t>GURIBEE BBQ BLDO 65G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20089490</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA PDS 90G</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20114757</t>
+  </si>
+  <si>
+    <t>GURIBEE RMP.LAUT 65G</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>20095753</t>
-  </si>
-  <si>
-    <t>GRUDA ROSTA WGYU 95</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -478,13 +472,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -544,15 +538,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -561,10 +555,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,7 +578,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,15 +598,15 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -621,30 +615,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20096682</t>
-  </si>
-  <si>
-    <t>IDM KACANG JUMBO 80</t>
+    <t>20122571</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PG 115G</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,58 +28,73 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20134572</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPRK 115</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20117928</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR SPCY2S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10036934</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 40G</t>
+    <t>20117923</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR ORI2'S</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20114756</t>
-  </si>
-  <si>
-    <t>GURIBEE BBQ BLDO 65G</t>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 104G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20114757</t>
-  </si>
-  <si>
-    <t>GURIBEE RMP.LAUT 65G</t>
+    <t>20140011</t>
+  </si>
+  <si>
+    <t>MILO BISC. CHOCO 96G</t>
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 104G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20140675</t>
+  </si>
+  <si>
+    <t>WINCHEEZ SPREAD 150G</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -472,13 +487,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -538,27 +553,27 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -578,7 +593,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -598,27 +613,67 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t/>
   </si>
   <si>
-    <t>20122571</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PG 115G</t>
+    <t>20139391</t>
+  </si>
+  <si>
+    <t>NEXTAR CHOC PIE 6S</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,73 +28,70 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20134572</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPRK 115</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140126</t>
+  </si>
+  <si>
+    <t>NEXTAR STRAWB CHS156</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20117928</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR SPCY2S</t>
+    <t>20136102</t>
+  </si>
+  <si>
+    <t>IDM SOES STROBERI80G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20117923</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR ORI2'S</t>
+    <t>20093909</t>
+  </si>
+  <si>
+    <t>REBO KUACI MILK 120</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20134969</t>
-  </si>
-  <si>
-    <t>MILO SANDW MILK 104G</t>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORIGNL120</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20140011</t>
-  </si>
-  <si>
-    <t>MILO BISC. CHOCO 96G</t>
+    <t>20068536</t>
+  </si>
+  <si>
+    <t>REBO KUACI G.TEA 120</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20134970</t>
-  </si>
-  <si>
-    <t>MILO SANDW ORIG 104G</t>
+    <t>20138272</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE SB 2X50</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20140675</t>
-  </si>
-  <si>
-    <t>WINCHEEZ SPREAD 150G</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>PT,(E-3B)</t>
   </si>
 </sst>
 </file>
@@ -550,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -558,122 +555,122 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20139391</t>
-  </si>
-  <si>
-    <t>NEXTAR CHOC PIE 6S</t>
+    <t>20097515</t>
+  </si>
+  <si>
+    <t>IDM POP CORN CRML 75</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -31,67 +31,67 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20140126</t>
-  </si>
-  <si>
-    <t>NEXTAR STRAWB CHS156</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
+    <t>20102071</t>
+  </si>
+  <si>
+    <t>IDM POPCRN SW.CHS 65</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20136102</t>
-  </si>
-  <si>
-    <t>IDM SOES STROBERI80G</t>
+    <t>20135539</t>
+  </si>
+  <si>
+    <t>MR.POTATO ORGINAL85G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20093909</t>
-  </si>
-  <si>
-    <t>REBO KUACI MILK 120</t>
+    <t>20136007</t>
+  </si>
+  <si>
+    <t>MR.POTATO BBQ 85G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20098348</t>
-  </si>
-  <si>
-    <t>REBO KUACI ORIGNL120</t>
+    <t>20135538</t>
+  </si>
+  <si>
+    <t>MR.POTATO SOUR&amp;O 85G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20068536</t>
-  </si>
-  <si>
-    <t>REBO KUACI G.TEA 120</t>
+    <t>10004490</t>
+  </si>
+  <si>
+    <t>HELLO PANDA STRW 42G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20138272</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE SB 2X50</t>
+    <t>10038704</t>
+  </si>
+  <si>
+    <t>MEIJI H/PANDA CHOC42</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
+    <t>20134559</t>
+  </si>
+  <si>
+    <t>HLO PANDA DB.CHO 42G</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -567,7 +567,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -575,10 +575,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -595,10 +595,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -615,10 +615,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -627,7 +627,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -635,10 +635,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -655,10 +655,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -667,10 +667,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
   <si>
     <t/>
   </si>
   <si>
-    <t>20097515</t>
-  </si>
-  <si>
-    <t>IDM POP CORN CRML 75</t>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 140</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,70 +28,61 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20102071</t>
-  </si>
-  <si>
-    <t>IDM POPCRN SW.CHS 65</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20072195</t>
+  </si>
+  <si>
+    <t>MH MAITOS JG.BBQ 140</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20135539</t>
-  </si>
-  <si>
-    <t>MR.POTATO ORGINAL85G</t>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20136007</t>
-  </si>
-  <si>
-    <t>MR.POTATO BBQ 85G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>20042370</t>
+  </si>
+  <si>
+    <t>M/SUKA R/LAUT PNG 9G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20135538</t>
-  </si>
-  <si>
-    <t>MR.POTATO SOUR&amp;O 85G</t>
+    <t>20073871</t>
+  </si>
+  <si>
+    <t>M/SUKA NORI PDS2X4.5</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10004490</t>
-  </si>
-  <si>
-    <t>HELLO PANDA STRW 42G</t>
+    <t>20097390</t>
+  </si>
+  <si>
+    <t>M/SUKA NORI BBQ2X4.5</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>10038704</t>
-  </si>
-  <si>
-    <t>MEIJI H/PANDA CHOC42</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20134559</t>
-  </si>
-  <si>
-    <t>HLO PANDA DB.CHO 42G</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
 </sst>
 </file>
@@ -484,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -570,15 +561,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -587,10 +578,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,7 +601,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,7 +621,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,27 +641,7 @@
         <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MH MAITOS S.BLDO 140</t>
+    <t>10002101</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHIP MRH140</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,61 +28,49 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20072195</t>
-  </si>
-  <si>
-    <t>MH MAITOS JG.BBQ 140</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10003485</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO ALMOND 52G</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10036987</t>
+  </si>
+  <si>
+    <t>S/Q CHOCO CASHEW 52G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
+    <t>20119019</t>
+  </si>
+  <si>
+    <t>HAPPYTOS HOT CHL 140</t>
+  </si>
+  <si>
+    <t>20023846</t>
+  </si>
+  <si>
+    <t>PRNGLES ORIGNAL 102G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20015338</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW CHSE 190</t>
-  </si>
-  <si>
-    <t>20042370</t>
-  </si>
-  <si>
-    <t>M/SUKA R/LAUT PNG 9G</t>
+    <t>20023845</t>
+  </si>
+  <si>
+    <t>PRINGLES CHEESY 102G</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>20073871</t>
-  </si>
-  <si>
-    <t>M/SUKA NORI PDS2X4.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20097390</t>
-  </si>
-  <si>
-    <t>M/SUKA NORI BBQ2X4.5</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
 </sst>
 </file>
@@ -475,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -538,10 +526,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,15 +549,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -581,15 +569,15 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -598,18 +586,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -618,30 +606,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>10002101</t>
-  </si>
-  <si>
-    <t>HAPPYTOS CHIP MRH140</t>
+    <t>20097515</t>
+  </si>
+  <si>
+    <t>IDM POPCRN CRML 75 G</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,49 +28,46 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
-  </si>
-  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES CKLT 80 G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20119019</t>
-  </si>
-  <si>
-    <t>HAPPYTOS HOT CHL 140</t>
-  </si>
-  <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORIGNAL 102G</t>
+    <t>20134456</t>
+  </si>
+  <si>
+    <t>JAP POCH UMJPS 115 G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHEESY 102G</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20012681</t>
+  </si>
+  <si>
+    <t>QTELA KRPK BBQ 175 G</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>20021029</t>
+  </si>
+  <si>
+    <t>QTELA KRPK BLD 175 G</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -463,13 +460,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -526,10 +523,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -549,15 +546,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -566,18 +563,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -586,30 +583,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t/>
   </si>
   <si>
-    <t>20097515</t>
-  </si>
-  <si>
-    <t>IDM POPCRN CRML 75 G</t>
+    <t>20073409</t>
+  </si>
+  <si>
+    <t>ROMA SANDW CKLT 157G</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -31,19 +31,19 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES CKLT 80 G</t>
+    <t>20098059</t>
+  </si>
+  <si>
+    <t>ROMA SNDW PEANUT 157</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20134456</t>
-  </si>
-  <si>
-    <t>JAP POCH UMJPS 115 G</t>
+    <t>20104942</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHOCO 50G</t>
   </si>
   <si>
     <t>3</t>
@@ -52,22 +52,46 @@
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20012681</t>
-  </si>
-  <si>
-    <t>QTELA KRPK BBQ 175 G</t>
+    <t>10011021</t>
+  </si>
+  <si>
+    <t>SIMBA CRL C/C COK 34</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20021029</t>
-  </si>
-  <si>
-    <t>QTELA KRPK BLD 175 G</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20113150</t>
+  </si>
+  <si>
+    <t>SIMBA CRL CC STRW 34</t>
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>20122975</t>
+  </si>
+  <si>
+    <t>CHOCOLITO RC.CHO 38G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20130543</t>
+  </si>
+  <si>
+    <t>CHOCOLITO ORGNL 38G</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -460,13 +484,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -566,15 +590,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -583,10 +607,50 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20073409</t>
-  </si>
-  <si>
-    <t>ROMA SANDW CKLT 157G</t>
+    <t>20045104</t>
+  </si>
+  <si>
+    <t>QTELA TEMPE CABE/R55</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,70 +28,58 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20033450</t>
+  </si>
+  <si>
+    <t>QTELA KRP/TMPE ORI55</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20056958</t>
+  </si>
+  <si>
+    <t>QTELA TEMPE R/LAUT55</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20042632</t>
+  </si>
+  <si>
+    <t>IDM KCG ATOM PDS 140</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20098059</t>
-  </si>
-  <si>
-    <t>ROMA SNDW PEANUT 157</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20104942</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHOCO 50G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10011021</t>
-  </si>
-  <si>
-    <t>SIMBA CRL C/C COK 34</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113150</t>
-  </si>
-  <si>
-    <t>SIMBA CRL CC STRW 34</t>
+    <t>20096682</t>
+  </si>
+  <si>
+    <t>IDM KACANG JUMBO 80</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20122975</t>
-  </si>
-  <si>
-    <t>CHOCOLITO RC.CHO 38G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20008798</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY CASHEW 82</t>
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20130543</t>
-  </si>
-  <si>
-    <t>CHOCOLITO ORGNL 38G</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -484,13 +472,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -570,15 +558,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -587,18 +575,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -607,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,27 +618,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t/>
   </si>
   <si>
-    <t>20045104</t>
-  </si>
-  <si>
-    <t>QTELA TEMPE CABE/R55</t>
+    <t>20097515</t>
+  </si>
+  <si>
+    <t>IDM POP CORN CRML 75</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,58 +28,64 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20033450</t>
-  </si>
-  <si>
-    <t>QTELA KRP/TMPE ORI55</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20102071</t>
+  </si>
+  <si>
+    <t>IDM POPCRN SW.CHS 65</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20056958</t>
-  </si>
-  <si>
-    <t>QTELA TEMPE R/LAUT55</t>
+    <t>20142232</t>
+  </si>
+  <si>
+    <t>IDM POPCRN CHOCO 65G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20042632</t>
-  </si>
-  <si>
-    <t>IDM KCG ATOM PDS 140</t>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20096682</t>
-  </si>
-  <si>
-    <t>IDM KACANG JUMBO 80</t>
+    <t>20140016</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHO PEANUT 37G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20008798</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
   </si>
   <si>
     <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2X50'S</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -472,16 +478,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,8 +507,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -517,11 +530,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -537,11 +550,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -557,11 +570,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -577,16 +590,16 @@
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,18 +608,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -615,10 +628,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t/>
   </si>
   <si>
-    <t>20097515</t>
-  </si>
-  <si>
-    <t>IDM POP CORN CRML 75</t>
+    <t>10026501</t>
+  </si>
+  <si>
+    <t>DK KACANG SUKRO 95G</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -31,61 +31,40 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20102071</t>
-  </si>
-  <si>
-    <t>IDM POPCRN SW.CHS 65</t>
+    <t>20084707</t>
+  </si>
+  <si>
+    <t>SUKRO KC OVEN BWG 95</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20142232</t>
-  </si>
-  <si>
-    <t>IDM POPCRN CHOCO 65G</t>
+    <t>20062966</t>
+  </si>
+  <si>
+    <t>DK SUKRO BBQ 95G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
+    <t>20134983</t>
+  </si>
+  <si>
+    <t>RITZ CRCKRS CHSE 91G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20140016</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHO PEANUT 37G</t>
+    <t>20022908</t>
+  </si>
+  <si>
+    <t>S/Q CHUNKY ALMOND 82</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20001061</t>
-  </si>
-  <si>
-    <t>MITU G/P PINK 2X50'S</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -478,17 +457,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,14 +485,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -530,11 +502,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -550,11 +522,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -570,11 +542,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -590,11 +562,11 @@
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -610,48 +582,8 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>10026501</t>
-  </si>
-  <si>
-    <t>DK KACANG SUKRO 95G</t>
+    <t>20124903</t>
+  </si>
+  <si>
+    <t>QTELA KR AY LD/HT100</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,40 +28,43 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20128427</t>
+  </si>
+  <si>
+    <t>QTELA KS RP.LAUT 100</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20140251</t>
+  </si>
+  <si>
+    <t>CHIKI P/C SALT CRM72</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20084707</t>
-  </si>
-  <si>
-    <t>SUKRO KC OVEN BWG 95</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20062966</t>
-  </si>
-  <si>
-    <t>DK SUKRO BBQ 95G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20134983</t>
-  </si>
-  <si>
-    <t>RITZ CRCKRS CHSE 91G</t>
+    <t>20139819</t>
+  </si>
+  <si>
+    <t>TANGO BROWNIS CR.35G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20022908</t>
-  </si>
-  <si>
-    <t>S/Q CHUNKY ALMOND 82</t>
+    <t>20096499</t>
+  </si>
+  <si>
+    <t>SMYANG AYM CRBO 130G</t>
   </si>
   <si>
     <t>5</t>
@@ -463,7 +466,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -543,15 +546,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -560,18 +563,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -580,10 +583,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
   <si>
     <t/>
   </si>
   <si>
-    <t>20124903</t>
-  </si>
-  <si>
-    <t>QTELA KR AY LD/HT100</t>
+    <t>10008550</t>
+  </si>
+  <si>
+    <t>G/T CHOCHP DB.CHO 72</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,46 +28,55 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20128427</t>
-  </si>
-  <si>
-    <t>QTELA KS RP.LAUT 100</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10008554</t>
+  </si>
+  <si>
+    <t>G/T CHOCOCHP CLSC 72</t>
+  </si>
+  <si>
+    <t>20062816</t>
+  </si>
+  <si>
+    <t>GT COOKIES RNBOW 72</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20140251</t>
-  </si>
-  <si>
-    <t>CHIKI P/C SALT CRM72</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20015338</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW CHSE 190</t>
+  </si>
+  <si>
+    <t>20120421</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 115G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139819</t>
-  </si>
-  <si>
-    <t>TANGO BROWNIS CR.35G</t>
+    <t>20126424</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 115G</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>20096499</t>
-  </si>
-  <si>
-    <t>SMYANG AYM CRBO 130G</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
 </sst>
 </file>
@@ -460,13 +469,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -523,7 +532,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -531,10 +540,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -543,18 +552,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -563,18 +572,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -583,10 +592,50 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU5AMKT.xlsx
+++ b/E/DU5AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20027448</t>
-  </si>
-  <si>
-    <t>TANGO WFR CHO 100 G</t>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
   </si>
   <si>
     <t>DU5AMKT</t>
@@ -28,46 +28,73 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10000442</t>
+  </si>
+  <si>
+    <t>FORTUNE MYK.GR R 2 L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20140913</t>
+  </si>
+  <si>
+    <t>SOVIA MNYK GR PCH1.8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20117923</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR ORI2'S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20111641</t>
-  </si>
-  <si>
-    <t>BETTER VANILLA 100 G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20047037</t>
-  </si>
-  <si>
-    <t>IDM KCANG BALI 150 G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20019479</t>
-  </si>
-  <si>
-    <t>N/SHIM SPCY M 120 G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20096499</t>
-  </si>
-  <si>
-    <t>SMYANG AYM CRB 130 G</t>
+    <t>20046198</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 51</t>
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 96G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 96G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20140011</t>
+  </si>
+  <si>
+    <t>MILO BISC. CHOCO 96G</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -460,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -546,27 +573,27 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -586,7 +613,67 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
